--- a/config/派單系統參數表.xlsx
+++ b/config/派單系統參數表.xlsx
@@ -10,6 +10,7 @@
     <sheet name="會員與優惠券" sheetId="5" r:id="rId5"/>
     <sheet name="系統參數" sheetId="6" r:id="rId6"/>
     <sheet name="司機資訊" sheetId="7" r:id="rId7"/>
+    <sheet name="允許群組白名單" sheetId="8" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
@@ -1378,17 +1379,6 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I6"/>
-  <cols>
-    <col min="1" max="1" width="36.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="25.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -1492,4 +1482,77 @@
     <ignoredError numberStoredAsText="1" sqref="A1:I6"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D4"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="str">
+        <v>允許群組白名單（司機接單群組）</v>
+      </c>
+      <c r="B1" s="1" t="str">
+        <v/>
+      </c>
+      <c r="C1" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D1" s="1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="str">
+        <v>群組名稱</v>
+      </c>
+      <c r="B2" s="1" t="str">
+        <v>LINE Group ID (groupId)</v>
+      </c>
+      <c r="C2" s="1" t="str">
+        <v>狀態 (active/inactive)</v>
+      </c>
+      <c r="D2" s="1" t="str">
+        <v>備註說明</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="str">
+        <v>派單測試群</v>
+      </c>
+      <c r="B3" s="1" t="str">
+        <v>C5179346ac8b2f3312cabe051ca818355</v>
+      </c>
+      <c r="C3" s="1" t="str">
+        <v>active</v>
+      </c>
+      <c r="D3" s="1" t="str">
+        <v>預設測試群組</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="str">
+        <v>正式司機一隊 (範例)</v>
+      </c>
+      <c r="B4" s="1" t="str">
+        <v>Cxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxx</v>
+      </c>
+      <c r="C4" s="1" t="str">
+        <v>inactive</v>
+      </c>
+      <c r="D4" s="1" t="str">
+        <v>待正式上線填入</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+  </ignoredErrors>
+</worksheet>
 </file>